--- a/BWI/bestwine_output/bestwine_Armenia.xlsx
+++ b/BWI/bestwine_output/bestwine_Armenia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3314,6 +3314,99 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Armenia</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour Armenia</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>106507</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Yerevan</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Yerevan</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>34 Arshakunyats Avenue</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0053</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://carrefour.am</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>info@carrefour.am</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>+374 11 300700</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carrefour-armenia/</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/carrefourarmenia/</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>Susanna Abrahamyan</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/susanna-abrahamyan-3245b32a9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
